--- a/TNP_Summer_Championships/SummerChamps.xlsx
+++ b/TNP_Summer_Championships/SummerChamps.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>3603411</v>
+        <v>3888984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -796,17 +796,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Craig Harris (SISU) </t>
+          <t>Dan Manalo (OTR)</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -817,22 +817,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SISU Racing</t>
+          <t>OTR Racing</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>35:09.218</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>01:52:52.095</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>31:29.854</t>
+        </is>
+      </c>
       <c r="K8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3440601</v>
+        <v>3603411</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -841,17 +845,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Berk Kayin [HEX]</t>
+          <t xml:space="preserve">Craig Harris (SISU) </t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -862,12 +866,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>HEXAGONE.CC</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>35:09.600</t>
+          <t>35:09.218</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -877,7 +881,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4297138</v>
+        <v>3440601</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -886,17 +890,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Thomas Nilsson [SZ]</t>
+          <t>Berk Kayin [HEX]</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -907,12 +911,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>HEXAGONE.CC</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>35:10.036</t>
+          <t>35:09.600</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -922,7 +926,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5997882</v>
+        <v>4297138</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -936,12 +940,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sigve V&amp;aring;gsnes</t>
+          <t>Thomas Nilsson [SZ]</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -952,12 +956,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>35:11.133</t>
+          <t>35:10.036</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -967,7 +971,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3440848</v>
+        <v>5997882</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -976,33 +980,33 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaan Kayin [HEX]</t>
+          <t>Sigve V&amp;aring;gsnes</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>2939</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>HEXAGONE.CC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>35:11.154</t>
+          <t>35:11.133</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1012,7 +1016,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>5408911</v>
+        <v>3440848</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1026,28 +1030,28 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Henry L</t>
+          <t>Kaan Kayin [HEX]</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2939</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>HEXAGONE.CC</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>35:11.807</t>
+          <t>35:11.154</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1057,7 +1061,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>432656</v>
+        <v>5408911</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1076,23 +1080,23 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Nick Baberuxki</t>
+          <t>Henry L</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>2848</v>
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Talent:frei p/b Baldiso</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>35:12.349</t>
+          <t>35:11.807</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
@@ -1102,7 +1106,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>7440439</v>
+        <v>432656</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1111,29 +1115,33 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Takahiro Nagayama</t>
+          <t>Nick Baberuxki</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>2848</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Talent:frei p/b Baldiso</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>35:16.617</t>
+          <t>35:12.349</t>
         </is>
       </c>
       <c r="J15" t="inlineStr"/>
@@ -1143,7 +1151,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4730842</v>
+        <v>7440439</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1152,7 +1160,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1162,23 +1170,19 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Harris Waters(ATGNI)</t>
+          <t>Takahiro Nagayama</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>2326</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>ATGNI</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>35:25.522</t>
+          <t>35:16.617</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
@@ -1188,7 +1192,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>399059</v>
+        <v>4730842</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1207,23 +1211,23 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Alan   Glendinning</t>
+          <t>Harris Waters(ATGNI)</t>
         </is>
       </c>
       <c r="F17" t="n">
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>2341</v>
+        <v>2326</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>LEVEL Esports</t>
+          <t>ATGNI</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>35:25.569</t>
+          <t>35:25.522</t>
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
@@ -1233,7 +1237,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1719043</v>
+        <v>399059</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1242,33 +1246,33 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dan Groom</t>
+          <t>Alan   Glendinning</t>
         </is>
       </c>
       <c r="F18" t="n">
         <v>1</v>
       </c>
       <c r="G18" t="n">
-        <v>2383</v>
+        <v>2341</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Njinga Cycling</t>
+          <t>LEVEL Esports</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>35:26.496</t>
+          <t>35:25.569</t>
         </is>
       </c>
       <c r="J18" t="inlineStr"/>
@@ -1278,7 +1282,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>706065</v>
+        <v>1719043</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1292,28 +1296,28 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Marzio Vanoni [TSE]</t>
+          <t>Dan Groom</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>2383</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>TSE</t>
+          <t>Njinga Cycling</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>35:29.830</t>
+          <t>35:26.496</t>
         </is>
       </c>
       <c r="J19" t="inlineStr"/>
@@ -1323,7 +1327,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7064533</v>
+        <v>706065</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1332,7 +1336,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1342,23 +1346,23 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Gregory Whitehead [A-PEX VELO]</t>
+          <t>Marzio Vanoni [TSE]</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>2377</v>
+        <v>0</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>TSE</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>35:35.635</t>
+          <t>35:29.830</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
@@ -1368,7 +1372,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1387591</v>
+        <v>7064533</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1382,28 +1386,28 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tommy Sellars (TFC Typhoon)</t>
+          <t>Gregory Whitehead [A-PEX VELO]</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>2377</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>TFC</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>35:44.079</t>
+          <t>35:35.635</t>
         </is>
       </c>
       <c r="J21" t="inlineStr"/>
@@ -1413,7 +1417,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2289407</v>
+        <v>1387591</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1422,7 +1426,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1432,7 +1436,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>A Aziz</t>
+          <t>Tommy Sellars (TFC Typhoon)</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1441,10 +1445,14 @@
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>TFC</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>35:57.713</t>
+          <t>35:44.079</t>
         </is>
       </c>
       <c r="J22" t="inlineStr"/>
@@ -1454,7 +1462,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5023963</v>
+        <v>2289407</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1468,28 +1476,24 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coach lak (TNP)</t>
+          <t>A Aziz</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>2092</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Team Not Pogi</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>36:10.833</t>
+          <t>35:57.713</t>
         </is>
       </c>
       <c r="J23" t="inlineStr"/>
@@ -1499,7 +1503,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2115767</v>
+        <v>5023963</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1513,28 +1517,28 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">J San Martino </t>
+          <t>Coach lak (TNP)</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>2092</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>ZABI</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>36:15.116</t>
+          <t>36:10.833</t>
         </is>
       </c>
       <c r="J24" t="inlineStr"/>
@@ -1544,7 +1548,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>383447</v>
+        <v>2115767</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1558,12 +1562,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Terry Wilkinson  (nopinzR3R)</t>
+          <t xml:space="preserve">J San Martino </t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1574,12 +1578,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>GTR E-Racing</t>
+          <t>ZABI</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>36:44.768</t>
+          <t>36:15.116</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
@@ -1589,7 +1593,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>397241</v>
+        <v>383447</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1598,7 +1602,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1608,7 +1612,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tom Williams</t>
+          <t>Terry Wilkinson  (nopinzR3R)</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1619,12 +1623,12 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Wahoo Esports</t>
+          <t>GTR E-Racing</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>37:15.642</t>
+          <t>36:44.768</t>
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
@@ -1634,7 +1638,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6807596</v>
+        <v>397241</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1643,7 +1647,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1653,7 +1657,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nichlas Broch-Lips [CVC]</t>
+          <t>Tom Williams</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1664,12 +1668,12 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Copenhagen Virtual Cycling</t>
+          <t>Wahoo Esports</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>37:38.251</t>
+          <t>37:15.642</t>
         </is>
       </c>
       <c r="J27" t="inlineStr"/>
@@ -1679,7 +1683,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>5189009</v>
+        <v>6807596</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1688,7 +1692,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1698,7 +1702,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Panu Kampor </t>
+          <t>Nichlas Broch-Lips [CVC]</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1709,12 +1713,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>WPJR - WhyPracticeJustRace</t>
+          <t>Copenhagen Virtual Cycling</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>37:44.424</t>
+          <t>37:38.251</t>
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
@@ -1724,7 +1728,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>176150</v>
+        <v>5189009</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1733,7 +1737,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1743,7 +1747,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>NAO TANI[EMU/TOMATO]3978</t>
+          <t xml:space="preserve">Panu Kampor </t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1754,12 +1758,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>EMU</t>
+          <t>WPJR - WhyPracticeJustRace</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>37:44.471</t>
+          <t>37:44.424</t>
         </is>
       </c>
       <c r="J29" t="inlineStr"/>
@@ -1769,7 +1773,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>5459336</v>
+        <v>176150</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1778,17 +1782,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Jnr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Nicholas Hanich</t>
+          <t>NAO TANI[EMU/TOMATO]3978</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1797,10 +1801,14 @@
       <c r="G30" t="n">
         <v>0</v>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>EMU</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>37:44.685</t>
+          <t>37:44.471</t>
         </is>
       </c>
       <c r="J30" t="inlineStr"/>
@@ -1810,7 +1818,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1898646</v>
+        <v>5459336</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1824,28 +1832,24 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Jnr</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Antoine</t>
+          <t>Nicholas Hanich</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>2106</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>37:50.351</t>
+          <t>37:44.685</t>
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
@@ -1855,7 +1859,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>679077</v>
+        <v>1898646</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1874,23 +1878,23 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Den Morrison</t>
+          <t>Antoine</t>
         </is>
       </c>
       <c r="F32" t="n">
         <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>2074</v>
+        <v>2106</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>DIRT</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>37:50.808</t>
+          <t>37:50.351</t>
         </is>
       </c>
       <c r="J32" t="inlineStr"/>
@@ -1900,7 +1904,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>526252</v>
+        <v>679077</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1914,24 +1918,28 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Carlos Amores (ZOSS VOG)(PTZ)</t>
+          <t>Den Morrison</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>2074</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>DIRT</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>38:11.875</t>
+          <t>37:50.808</t>
         </is>
       </c>
       <c r="J33" t="inlineStr"/>
@@ -1941,7 +1949,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>628179</v>
+        <v>526252</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1950,7 +1958,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1960,7 +1968,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Matt Davison</t>
+          <t>Carlos Amores (ZOSS VOG)(PTZ)</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1969,14 +1977,10 @@
       <c r="G34" t="n">
         <v>0</v>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Valhalla</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>46:23.195</t>
+          <t>38:11.875</t>
         </is>
       </c>
       <c r="J34" t="inlineStr"/>
@@ -1986,7 +1990,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>25864</v>
+        <v>628179</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -2000,28 +2004,28 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Michael Mansfield</t>
+          <t>Matt Davison</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>3075</v>
+        <v>0</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Team CRYO-GEN</t>
+          <t>Valhalla</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>46:36.087</t>
+          <t>46:23.195</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -2031,7 +2035,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>57852</v>
+        <v>25864</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -2050,23 +2054,23 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Alan Lowe</t>
+          <t>Michael Mansfield</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>3075</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>TURBO</t>
+          <t>Team CRYO-GEN</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>46:36.170</t>
+          <t>46:36.087</t>
         </is>
       </c>
       <c r="J36" t="inlineStr"/>
@@ -2076,7 +2080,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>4999942</v>
+        <v>57852</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -2085,17 +2089,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Tor Bendiksen</t>
+          <t>Alan Lowe</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -2106,12 +2110,12 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Beastmode</t>
+          <t>TURBO</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>46:36.312</t>
+          <t>46:36.170</t>
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
@@ -2121,7 +2125,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>795625</v>
+        <v>4999942</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -2130,7 +2134,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2140,23 +2144,23 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Mike Saunders (OTR)</t>
+          <t>Tor Bendiksen</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2667</v>
+        <v>0</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>OTR Racing</t>
+          <t>Beastmode</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>46:36.374</t>
+          <t>46:36.312</t>
         </is>
       </c>
       <c r="J38" t="inlineStr"/>
@@ -2166,7 +2170,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1387754</v>
+        <v>795625</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -2180,28 +2184,28 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Tommy  Lawrence (CC)</t>
+          <t>Mike Saunders (OTR)</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>2667</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">CC </t>
+          <t>OTR Racing</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>46:36.844</t>
+          <t>46:36.374</t>
         </is>
       </c>
       <c r="J39" t="inlineStr"/>
@@ -2211,7 +2215,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>711180</v>
+        <v>1387754</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -2225,28 +2229,28 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Jan [CCC]</t>
+          <t>Tommy  Lawrence (CC)</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>2700</v>
+        <v>0</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>ZLDR</t>
+          <t xml:space="preserve">CC </t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>46:36.896</t>
+          <t>46:36.844</t>
         </is>
       </c>
       <c r="J40" t="inlineStr"/>
@@ -2256,7 +2260,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>733964</v>
+        <v>711180</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -2270,24 +2274,28 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mark Chong </t>
+          <t>Jan [CCC]</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>2700</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>ZLDR</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>46:57.529</t>
+          <t>46:36.896</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -2297,7 +2305,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>4980720</v>
+        <v>733964</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -2311,28 +2319,24 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Christopher Keogh [eSRT]</t>
+          <t xml:space="preserve">Mark Chong </t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>2960</v>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>eSRT</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>47:08.972</t>
+          <t>46:57.529</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -2342,7 +2346,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>700758</v>
+        <v>4980720</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2351,33 +2355,33 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>wout vervoort[WATT]</t>
+          <t>Christopher Keogh [eSRT]</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>2960</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>The Watt Squad</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>47:30.465</t>
+          <t>47:08.972</t>
         </is>
       </c>
       <c r="J43" t="inlineStr"/>
@@ -2387,7 +2391,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1604082</v>
+        <v>700758</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2401,12 +2405,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Alexandre Doyon | V&amp;eacute;lo Optimum</t>
+          <t>wout vervoort[WATT]</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2417,12 +2421,12 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Optimum</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>47:33.122</t>
+          <t>47:30.465</t>
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
@@ -2432,7 +2436,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>5694958</v>
+        <v>1604082</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2441,7 +2445,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2451,7 +2455,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nic Bathgate (eSRT/4STAR)</t>
+          <t>Alexandre Doyon | V&amp;eacute;lo Optimum</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2462,12 +2466,12 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>Optimum</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>48:14.137</t>
+          <t>47:33.122</t>
         </is>
       </c>
       <c r="J45" t="inlineStr"/>
@@ -2477,7 +2481,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>723953</v>
+        <v>5694958</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2486,7 +2490,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2496,7 +2500,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chris Koch | ZwiftRaceCraft | YouTube </t>
+          <t>Nic Bathgate (eSRT/4STAR)</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2507,12 +2511,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>COALITION</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>48:35.767</t>
+          <t>48:14.137</t>
         </is>
       </c>
       <c r="J46" t="inlineStr"/>
@@ -2522,7 +2526,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3605728</v>
+        <v>723953</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2531,33 +2535,33 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Steven Garr&amp;eacute; [WATT]</t>
+          <t xml:space="preserve">Chris Koch | ZwiftRaceCraft | YouTube </t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>2358</v>
+        <v>0</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>The Watt Squad</t>
+          <t>COALITION</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>49:28.351</t>
+          <t>48:35.767</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
@@ -2567,7 +2571,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>4145236</v>
+        <v>3605728</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2576,7 +2580,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2586,23 +2590,23 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mathias M. B.  [CVC] </t>
+          <t>Steven Garr&amp;eacute; [WATT]</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>2358</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Copenhagen Virtual Cycling</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>49:41.768</t>
+          <t>49:28.351</t>
         </is>
       </c>
       <c r="J48" t="inlineStr"/>
@@ -2612,7 +2616,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>3888984</v>
+        <v>4145236</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2626,12 +2630,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dan Manalo (OTR)</t>
+          <t xml:space="preserve">Mathias M. B.  [CVC] </t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2642,12 +2646,12 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>OTR Racing</t>
+          <t>Copenhagen Virtual Cycling</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50:23.990</t>
+          <t>49:41.768</t>
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
@@ -6458,7 +6462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6791,16 +6795,16 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>619770</v>
+        <v>3888984</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6810,34 +6814,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert McEwan </t>
+          <t>Dan Manalo (OTR)</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>1853</v>
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>OTR Racing</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>31:29.854</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>01:27:59.196</t>
+          <t>01:52:52.095</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>374410</v>
+        <v>619770</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -6846,28 +6850,28 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jnr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Tom Ross  (TNP)</t>
+          <t xml:space="preserve">Robert McEwan </t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>1916</v>
+        <v>1853</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>BIKELY</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -6877,13 +6881,13 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>01:28:33.056</t>
+          <t>01:27:59.196</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1511742</v>
+        <v>374410</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -6892,44 +6896,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Jnr</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mark Hayes [PWCC]</t>
+          <t>Tom Ross  (TNP)</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>1958</v>
+        <v>1916</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>BIKELY</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>35.080</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>01:28:34.276</t>
+          <t>01:28:33.056</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>372647</v>
+        <v>1511742</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -6938,7 +6942,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -6948,34 +6952,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>PA Persson [AAC]</t>
+          <t>Mark Hayes [PWCC]</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1958</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>01:00.879</t>
+          <t>35.080</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>01:29:33.935</t>
+          <t>01:28:34.276</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7799511</v>
+        <v>372647</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -6994,38 +6998,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>PA Persson [AAC]</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>1607</v>
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>AAC</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>06:40.058</t>
+          <t>01:00.879</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>01:34:39.254</t>
+          <t>01:29:33.935</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6038763</v>
+        <v>7799511</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -7035,39 +7039,39 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Spartacus [CVC]</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1607</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Copenhagen Virtual Cycling</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>06:40.058</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>01:28:51.715</t>
+          <t>01:34:39.254</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6832982</v>
+        <v>6038763</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -7081,12 +7085,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ben WillRideForDonuts (4Star)</t>
+          <t>Spartacus [CVC]</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -7097,7 +7101,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">4STAR </t>
+          <t>Copenhagen Virtual Cycling</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -7107,13 +7111,13 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>01:31:48.608</t>
+          <t>01:28:51.715</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>72072</v>
+        <v>6832982</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -7127,35 +7131,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2. Burrito &amp;#127791;</t>
+          <t xml:space="preserve"> Ben WillRideForDonuts (4Star)</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1583</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4STAR </t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>04.873</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>01:31:53.481</t>
+          <t>01:31:48.608</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4166463</v>
+        <v>72072</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -7164,7 +7172,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -7174,30 +7182,30 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
+          <t>2. Burrito &amp;#127791;</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>1376</v>
+        <v>1583</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>33.992</t>
+          <t>04.873</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>01:32:22.600</t>
+          <t>01:31:53.481</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>440496</v>
+        <v>4166463</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -7206,44 +7214,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Magnus  Andersson [SZ]</t>
+          <t>Corey Green (YT) GarageCycling</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>SZ</t>
-        </is>
-      </c>
+        <v>1376</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>04:15.024</t>
+          <t>33.992</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>01:33:06.739</t>
+          <t>01:32:22.600</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6991072</v>
+        <v>440496</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -7252,7 +7256,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -7262,34 +7266,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jorge Fernandez Fernandez</t>
+          <t>Magnus  Andersson [SZ]</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1341</v>
+        <v>0</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>06:45.171</t>
+          <t>04:15.024</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>01:37:01.020</t>
+          <t>01:33:06.739</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1005102</v>
+        <v>6991072</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -7298,7 +7302,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -7308,34 +7312,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t>Jorge Fernandez Fernandez</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>1515</v>
+        <v>1341</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>06:14.623</t>
+          <t>06:45.171</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>01:38:03.231</t>
+          <t>01:37:01.020</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2602856</v>
+        <v>1005102</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -7349,85 +7353,85 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" t="n">
-        <v>1394</v>
+        <v>1515</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>09:32.832</t>
+          <t>06:14.623</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>01:38:24.547</t>
+          <t>01:38:03.231</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1563175</v>
+        <v>2602856</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AL C SimpSimpHea</t>
+          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>1149</v>
+        <v>1394</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>09:32.832</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>01:36:13.852</t>
+          <t>01:38:24.547</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2692261</v>
+        <v>1563175</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -7441,19 +7445,19 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Murray Irons</t>
+          <t>AL C SimpSimpHea</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1149</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -7462,18 +7466,18 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>35.240</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>01:36:49.092</t>
+          <t>01:36:13.852</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>832585</v>
+        <v>2692261</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -7487,19 +7491,19 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>Murray Irons</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>886</v>
+        <v>0</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -7508,18 +7512,18 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>01:19.277</t>
+          <t>35.240</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>01:37:33.129</t>
+          <t>01:36:49.092</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6513233</v>
+        <v>832585</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -7533,19 +7537,19 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim YUU </t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="F24" t="n">
         <v>8</v>
       </c>
       <c r="G24" t="n">
-        <v>909</v>
+        <v>886</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -7554,18 +7558,18 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>01:55.047</t>
+          <t>01:19.277</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>01:38:08.899</t>
+          <t>01:37:33.129</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6547311</v>
+        <v>6513233</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -7574,7 +7578,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7584,14 +7588,14 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jimi Miralles-Lombardo</t>
+          <t xml:space="preserve">Kim YUU </t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>909</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -7600,18 +7604,18 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>02:33.837</t>
+          <t>01:55.047</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>01:38:47.689</t>
+          <t>01:38:08.899</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7779078</v>
+        <v>6547311</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -7620,24 +7624,24 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>David Irwin</t>
+          <t>Jimi Miralles-Lombardo</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1087</v>
+        <v>0</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -7646,18 +7650,18 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>05:25.447</t>
+          <t>02:33.837</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>01:41:39.299</t>
+          <t>01:38:47.689</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7853050</v>
+        <v>7779078</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -7676,14 +7680,14 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Talyn Portman [HERC]  &amp;#6560; &amp;#127922;</t>
+          <t>David Irwin</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>1087</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -7692,18 +7696,18 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>08:44.381</t>
+          <t>05:25.447</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>01:44:58.233</t>
+          <t>01:41:39.299</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1475359</v>
+        <v>7853050</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -7722,72 +7726,118 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Andy Morton (TNP)</t>
+          <t>Talyn Portman [HERC]  &amp;#6560; &amp;#127922;</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>904</v>
+        <v>0</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>08:44.381</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>01:46:13.108</t>
+          <t>01:44:58.233</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
+        <v>1475359</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>50+</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Andy Morton (TNP)</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>8</v>
+      </c>
+      <c r="G29" t="n">
+        <v>904</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>00.000</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>01:46:13.108</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
         <v>8233611</v>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Vet</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>Benjamin Breakfast [HERC]</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" t="inlineStr">
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>HERC</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>00.000</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>01:50:33.790</t>
         </is>
@@ -7944,12 +7994,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HEXAGONE.CC</t>
+          <t>OTR Racing</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>01:10:20.754</t>
+          <t>02:39:28.469</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -7958,23 +8008,23 @@
         </is>
       </c>
       <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>01:37:00.364</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>00.000</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>01:10:20.754</t>
+          <t>01:02:28.105</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -7985,12 +8035,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A-P-V</t>
+          <t>HEXAGONE.CC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>01:10:47.442</t>
+          <t>01:10:20.754</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -8011,7 +8061,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>01:10:47.442</t>
+          <t>01:10:20.754</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -8026,12 +8076,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TEZH Racing</t>
+          <t>A-P-V</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>01:21:48.628</t>
+          <t>01:10:47.442</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -8044,19 +8094,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>46:36.826</t>
+          <t>00.000</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>35:11.802</t>
+          <t>01:10:47.442</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -8067,12 +8117,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.W.4.T</t>
+          <t>TEZH Racing</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>01:24:11.494</t>
+          <t>01:21:48.628</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -8085,7 +8135,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>48:06.707</t>
+          <t>46:36.826</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -8093,7 +8143,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>36:04.787</t>
+          <t>35:11.802</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -8108,12 +8158,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Copenhagen Virtual Cycling</t>
+          <t>5.W.4.T</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>01:27:20.019</t>
+          <t>01:24:11.494</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -8126,7 +8176,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>49:41.768</t>
+          <t>48:06.707</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -8134,7 +8184,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>37:38.251</t>
+          <t>36:04.787</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -8149,12 +8199,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Team CLS</t>
+          <t>Copenhagen Virtual Cycling</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>01:35:28.531</t>
+          <t>01:27:20.019</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -8167,7 +8217,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>54:00.320</t>
+          <t>49:41.768</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -8175,7 +8225,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>41:28.211</t>
+          <t>37:38.251</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -8190,12 +8240,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Watt Squad</t>
+          <t>Team CLS</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>01:36:58.816</t>
+          <t>01:35:28.531</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8208,19 +8258,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>01:36:58.816</t>
+          <t>54:00.320</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>00.000</t>
+          <t>41:28.211</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -8231,12 +8281,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OTR Racing</t>
+          <t>The Watt Squad</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>01:37:00.364</t>
+          <t>01:36:58.816</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8249,7 +8299,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>01:37:00.364</t>
+          <t>01:36:58.816</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -10735,7 +10785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
+  <dimension ref="A1:R30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10832,7 +10882,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1299505</v>
+        <v>3888984</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -10846,34 +10896,34 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Laurent LeBel [5.W.4.T]</t>
+          <t>Dan Manalo (OTR)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.W.4.T</t>
+          <t>OTR Racing</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G2" t="n">
         <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>10.979</v>
+        <v>10.419</v>
       </c>
       <c r="I2" t="n">
-        <v>16.24</v>
+        <v>16.633</v>
       </c>
       <c r="J2" t="n">
-        <v>19.866</v>
+        <v>19.279</v>
       </c>
       <c r="K2" t="n">
-        <v>10.509</v>
+        <v>9.118</v>
       </c>
       <c r="L2" t="n">
-        <v>23.977</v>
+        <v>23.387</v>
       </c>
       <c r="M2" t="n">
         <v>20</v>
@@ -10882,19 +10932,19 @@
         <v>20</v>
       </c>
       <c r="O2" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="P2" t="n">
         <v>20</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="R2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>599879</v>
+        <v>1299505</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -10903,60 +10953,60 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>J.MORENO (TEZH RACING)</t>
+          <t>Laurent LeBel [5.W.4.T]</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TEZH Racing</t>
+          <t>5.W.4.T</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>13.74</v>
+        <v>10.979</v>
       </c>
       <c r="I3" t="n">
-        <v>18.994</v>
+        <v>16.24</v>
       </c>
       <c r="J3" t="n">
-        <v>20.58</v>
+        <v>19.866</v>
       </c>
       <c r="K3" t="n">
-        <v>9.318</v>
+        <v>10.509</v>
       </c>
       <c r="L3" t="n">
-        <v>26.86</v>
+        <v>23.977</v>
       </c>
       <c r="M3" t="n">
         <v>18</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O3" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="P3" t="n">
         <v>18</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5893609</v>
+        <v>599879</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -10965,60 +11015,60 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Aled Jones</t>
+          <t>J.MORENO (TEZH RACING)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>TEZH Racing</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="G4" t="n">
         <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>12.407</v>
+        <v>13.74</v>
       </c>
       <c r="I4" t="n">
-        <v>18.592</v>
+        <v>18.994</v>
       </c>
       <c r="J4" t="n">
-        <v>22.06</v>
+        <v>20.58</v>
       </c>
       <c r="K4" t="n">
-        <v>11.072</v>
+        <v>9.318</v>
       </c>
       <c r="L4" t="n">
-        <v>27.092</v>
+        <v>26.86</v>
       </c>
       <c r="M4" t="n">
         <v>16</v>
       </c>
       <c r="N4" t="n">
+        <v>10</v>
+      </c>
+      <c r="O4" t="n">
         <v>18</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q4" t="n">
         <v>12</v>
-      </c>
-      <c r="P4" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>18</v>
       </c>
       <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>6853346</v>
+        <v>5893609</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -11027,12 +11077,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>A+</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Matthieu De Smet </t>
+          <t>Aled Jones</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -11041,34 +11091,34 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="G5" t="n">
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>13.571</v>
+        <v>12.407</v>
       </c>
       <c r="I5" t="n">
-        <v>18.802</v>
+        <v>18.592</v>
       </c>
       <c r="J5" t="n">
-        <v>22.36</v>
+        <v>22.06</v>
       </c>
       <c r="K5" t="n">
-        <v>10.447</v>
+        <v>11.072</v>
       </c>
       <c r="L5" t="n">
-        <v>27.956</v>
+        <v>27.092</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
       </c>
       <c r="N5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O5" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="P5" t="n">
         <v>12</v>
@@ -11080,7 +11130,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1215790</v>
+        <v>6853346</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -11089,60 +11139,60 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>A+</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jan Lichtwark </t>
+          <t xml:space="preserve">Matthieu De Smet </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>eSRT</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
         <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>12.599</v>
+        <v>13.571</v>
       </c>
       <c r="I6" t="n">
-        <v>19.666</v>
+        <v>18.802</v>
       </c>
       <c r="J6" t="n">
-        <v>21.151</v>
+        <v>22.36</v>
       </c>
       <c r="K6" t="n">
-        <v>10.734</v>
+        <v>10.447</v>
       </c>
       <c r="L6" t="n">
-        <v>28.517</v>
+        <v>27.956</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
       </c>
       <c r="N6" t="n">
+        <v>12</v>
+      </c>
+      <c r="O6" t="n">
         <v>16</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q6" t="n">
         <v>14</v>
-      </c>
-      <c r="P6" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>12</v>
       </c>
       <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>561362</v>
+        <v>1215790</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -11156,46 +11206,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The Inevitable Return of the Great White Dope</t>
+          <t xml:space="preserve">Jan Lichtwark </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Team CLS</t>
+          <t>eSRT</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>14.984</v>
+        <v>12.599</v>
       </c>
       <c r="I7" t="n">
-        <v>22.959</v>
+        <v>19.666</v>
       </c>
       <c r="J7" t="n">
-        <v>26.105</v>
+        <v>21.151</v>
       </c>
       <c r="K7" t="n">
-        <v>11.525</v>
+        <v>10.734</v>
       </c>
       <c r="L7" t="n">
-        <v>31.71</v>
+        <v>28.517</v>
       </c>
       <c r="M7" t="n">
         <v>10</v>
       </c>
       <c r="N7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="O7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="Q7" t="n">
         <v>10</v>
@@ -11204,69 +11254,69 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7799511</v>
+        <v>561362</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>The Inevitable Return of the Great White Dope</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>Team CLS</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>12.366</v>
+        <v>14.984</v>
       </c>
       <c r="I8" t="n">
-        <v>15.814</v>
+        <v>22.959</v>
       </c>
       <c r="J8" t="n">
-        <v>19.266</v>
+        <v>26.105</v>
       </c>
       <c r="K8" t="n">
-        <v>9.619</v>
+        <v>11.525</v>
       </c>
       <c r="L8" t="n">
-        <v>22.488</v>
+        <v>31.71</v>
       </c>
       <c r="M8" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="O8" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="P8" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>374410</v>
+        <v>7799511</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -11280,55 +11330,55 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tom Ross  (TNP)</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BIKELY</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>15.359</v>
+        <v>12.366</v>
       </c>
       <c r="I9" t="n">
-        <v>18.88</v>
+        <v>15.814</v>
       </c>
       <c r="J9" t="n">
-        <v>23.12</v>
+        <v>19.266</v>
       </c>
       <c r="K9" t="n">
-        <v>12.399</v>
+        <v>9.619</v>
       </c>
       <c r="L9" t="n">
-        <v>26.038</v>
+        <v>22.488</v>
       </c>
       <c r="M9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N9" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O9" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="P9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>619770</v>
+        <v>374410</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -11337,60 +11387,60 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert McEwan </t>
+          <t>Tom Ross  (TNP)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>BIKELY</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>13.037</v>
+        <v>15.359</v>
       </c>
       <c r="I10" t="n">
-        <v>19.34</v>
+        <v>18.88</v>
       </c>
       <c r="J10" t="n">
-        <v>25.501</v>
+        <v>23.12</v>
       </c>
       <c r="K10" t="n">
-        <v>11.807</v>
+        <v>12.399</v>
       </c>
       <c r="L10" t="n">
-        <v>28.979</v>
+        <v>26.038</v>
       </c>
       <c r="M10" t="n">
+        <v>18</v>
+      </c>
+      <c r="N10" t="n">
+        <v>14</v>
+      </c>
+      <c r="O10" t="n">
         <v>12</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>18</v>
       </c>
-      <c r="O10" t="n">
-        <v>14</v>
-      </c>
-      <c r="P10" t="n">
-        <v>14</v>
-      </c>
       <c r="Q10" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>372647</v>
+        <v>619770</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -11399,17 +11449,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PA Persson [AAC]</t>
+          <t xml:space="preserve">Robert McEwan </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -11419,40 +11469,40 @@
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>16.702</v>
+        <v>13.037</v>
       </c>
       <c r="I11" t="n">
-        <v>23.336</v>
+        <v>19.34</v>
       </c>
       <c r="J11" t="n">
-        <v>24.833</v>
+        <v>25.501</v>
       </c>
       <c r="K11" t="n">
-        <v>11.366</v>
+        <v>11.807</v>
       </c>
       <c r="L11" t="n">
-        <v>28.263</v>
+        <v>28.979</v>
       </c>
       <c r="M11" t="n">
+        <v>12</v>
+      </c>
+      <c r="N11" t="n">
+        <v>18</v>
+      </c>
+      <c r="O11" t="n">
+        <v>14</v>
+      </c>
+      <c r="P11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q11" t="n">
         <v>16</v>
-      </c>
-      <c r="N11" t="n">
-        <v>12</v>
-      </c>
-      <c r="O11" t="n">
-        <v>18</v>
-      </c>
-      <c r="P11" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>12</v>
       </c>
       <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1511742</v>
+        <v>372647</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -11461,122 +11511,122 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Mark Hayes [PWCC]</t>
+          <t>PA Persson [AAC]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>AAC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>13.853</v>
+        <v>16.702</v>
       </c>
       <c r="I12" t="n">
-        <v>20.232</v>
+        <v>23.336</v>
       </c>
       <c r="J12" t="n">
-        <v>25.617</v>
+        <v>24.833</v>
       </c>
       <c r="K12" t="n">
-        <v>11.742</v>
+        <v>11.366</v>
       </c>
       <c r="L12" t="n">
-        <v>28.529</v>
+        <v>28.263</v>
       </c>
       <c r="M12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N12" t="n">
+        <v>12</v>
+      </c>
+      <c r="O12" t="n">
+        <v>18</v>
+      </c>
+      <c r="P12" t="n">
         <v>16</v>
       </c>
-      <c r="O12" t="n">
-        <v>16</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>12</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>14</v>
       </c>
       <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6038763</v>
+        <v>1511742</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Spartacus [CVC]</t>
+          <t>Mark Hayes [PWCC]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copenhagen Virtual Cycling</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>92</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>13.199</v>
+        <v>13.853</v>
       </c>
       <c r="I13" t="n">
-        <v>19.52</v>
+        <v>20.232</v>
       </c>
       <c r="J13" t="n">
-        <v>24.201</v>
+        <v>25.617</v>
       </c>
       <c r="K13" t="n">
-        <v>11.479</v>
+        <v>11.742</v>
       </c>
       <c r="L13" t="n">
-        <v>27.2</v>
+        <v>28.529</v>
       </c>
       <c r="M13" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="N13" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O13" t="n">
+        <v>16</v>
+      </c>
+      <c r="P13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q13" t="n">
         <v>14</v>
-      </c>
-      <c r="P13" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>20</v>
       </c>
       <c r="R13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>440496</v>
+        <v>6038763</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -11590,55 +11640,55 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Magnus  Andersson [SZ]</t>
+          <t>Spartacus [CVC]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SZ</t>
+          <t>Copenhagen Virtual Cycling</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>13.881</v>
+        <v>13.199</v>
       </c>
       <c r="I14" t="n">
-        <v>22.582</v>
+        <v>19.52</v>
       </c>
       <c r="J14" t="n">
-        <v>22.284</v>
+        <v>24.201</v>
       </c>
       <c r="K14" t="n">
-        <v>10.828</v>
+        <v>11.479</v>
       </c>
       <c r="L14" t="n">
-        <v>31.005</v>
+        <v>27.2</v>
       </c>
       <c r="M14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N14" t="n">
+        <v>20</v>
+      </c>
+      <c r="O14" t="n">
+        <v>14</v>
+      </c>
+      <c r="P14" t="n">
         <v>18</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>20</v>
-      </c>
-      <c r="P14" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>16</v>
       </c>
       <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1005102</v>
+        <v>440496</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -11652,55 +11702,55 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t>Magnus  Andersson [SZ]</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>18.121</v>
+        <v>13.881</v>
       </c>
       <c r="I15" t="n">
-        <v>21.221</v>
+        <v>22.582</v>
       </c>
       <c r="J15" t="n">
-        <v>25.94</v>
+        <v>22.284</v>
       </c>
       <c r="K15" t="n">
-        <v>11.166</v>
+        <v>10.828</v>
       </c>
       <c r="L15" t="n">
-        <v>31.43</v>
+        <v>31.005</v>
       </c>
       <c r="M15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="O15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P15" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q15" t="n">
         <v>16</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>18</v>
       </c>
       <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6991072</v>
+        <v>1005102</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -11709,60 +11759,60 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Jorge Fernandez Fernandez</t>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>15.928</v>
+        <v>18.121</v>
       </c>
       <c r="I16" t="n">
-        <v>24.141</v>
+        <v>21.221</v>
       </c>
       <c r="J16" t="n">
-        <v>28.113</v>
+        <v>25.94</v>
       </c>
       <c r="K16" t="n">
-        <v>12.085</v>
+        <v>11.166</v>
       </c>
       <c r="L16" t="n">
-        <v>27.737</v>
+        <v>31.43</v>
       </c>
       <c r="M16" t="n">
+        <v>14</v>
+      </c>
+      <c r="N16" t="n">
+        <v>8</v>
+      </c>
+      <c r="O16" t="n">
         <v>18</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>16</v>
       </c>
-      <c r="O16" t="n">
-        <v>8</v>
-      </c>
-      <c r="P16" t="n">
-        <v>8</v>
-      </c>
       <c r="Q16" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6832982</v>
+        <v>6991072</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -11771,60 +11821,60 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ben WillRideForDonuts (4Star)</t>
+          <t>Jorge Fernandez Fernandez</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">4STAR </t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>16.195</v>
+        <v>15.928</v>
       </c>
       <c r="I17" t="n">
-        <v>23.761</v>
+        <v>24.141</v>
       </c>
       <c r="J17" t="n">
-        <v>26.928</v>
+        <v>28.113</v>
       </c>
       <c r="K17" t="n">
-        <v>11.779</v>
+        <v>12.085</v>
       </c>
       <c r="L17" t="n">
-        <v>34.016</v>
+        <v>27.737</v>
       </c>
       <c r="M17" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="O17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="P17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>72072</v>
+        <v>6832982</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -11838,10 +11888,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2. Burrito &amp;#127791;</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
+          <t xml:space="preserve"> Ben WillRideForDonuts (4Star)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4STAR </t>
+        </is>
+      </c>
       <c r="F18" t="n">
         <v>56</v>
       </c>
@@ -11849,40 +11903,40 @@
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>16.765</v>
+        <v>16.195</v>
       </c>
       <c r="I18" t="n">
-        <v>23.532</v>
+        <v>23.761</v>
       </c>
       <c r="J18" t="n">
-        <v>26.602</v>
+        <v>26.928</v>
       </c>
       <c r="K18" t="n">
-        <v>11.933</v>
+        <v>11.779</v>
       </c>
       <c r="L18" t="n">
-        <v>34.215</v>
+        <v>34.016</v>
       </c>
       <c r="M18" t="n">
+        <v>12</v>
+      </c>
+      <c r="N18" t="n">
+        <v>12</v>
+      </c>
+      <c r="O18" t="n">
+        <v>12</v>
+      </c>
+      <c r="P18" t="n">
         <v>10</v>
       </c>
-      <c r="N18" t="n">
-        <v>9</v>
-      </c>
-      <c r="O18" t="n">
-        <v>9</v>
-      </c>
-      <c r="P18" t="n">
-        <v>14</v>
-      </c>
       <c r="Q18" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2602856</v>
+        <v>72072</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -11896,14 +11950,10 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
-        </is>
-      </c>
+          <t>2. Burrito &amp;#127791;</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="n">
         <v>56</v>
       </c>
@@ -11911,40 +11961,40 @@
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>16.008</v>
+        <v>16.765</v>
       </c>
       <c r="I19" t="n">
-        <v>24.007</v>
+        <v>23.532</v>
       </c>
       <c r="J19" t="n">
-        <v>27.912</v>
+        <v>26.602</v>
       </c>
       <c r="K19" t="n">
-        <v>11.23</v>
+        <v>11.933</v>
       </c>
       <c r="L19" t="n">
-        <v>35.091</v>
+        <v>34.215</v>
       </c>
       <c r="M19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
+        <v>9</v>
+      </c>
+      <c r="O19" t="n">
+        <v>9</v>
+      </c>
+      <c r="P19" t="n">
         <v>14</v>
       </c>
-      <c r="O19" t="n">
-        <v>16</v>
-      </c>
-      <c r="P19" t="n">
-        <v>9</v>
-      </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="R19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>4166463</v>
+        <v>2602856</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -11953,60 +12003,64 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
+          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+        </is>
+      </c>
       <c r="F20" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>16.693</v>
+        <v>16.008</v>
       </c>
       <c r="I20" t="n">
-        <v>23.715</v>
+        <v>24.007</v>
       </c>
       <c r="J20" t="n">
-        <v>26.926</v>
+        <v>27.912</v>
       </c>
       <c r="K20" t="n">
-        <v>11.851</v>
+        <v>11.23</v>
       </c>
       <c r="L20" t="n">
-        <v>34.329</v>
+        <v>35.091</v>
       </c>
       <c r="M20" t="n">
+        <v>8</v>
+      </c>
+      <c r="N20" t="n">
+        <v>14</v>
+      </c>
+      <c r="O20" t="n">
+        <v>16</v>
+      </c>
+      <c r="P20" t="n">
         <v>9</v>
       </c>
-      <c r="N20" t="n">
-        <v>10</v>
-      </c>
-      <c r="O20" t="n">
-        <v>10</v>
-      </c>
-      <c r="P20" t="n">
-        <v>12</v>
-      </c>
       <c r="Q20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="R20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1563175</v>
+        <v>4166463</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -12016,55 +12070,51 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AL C SimpSimpHea</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Corey Green (YT) GarageCycling</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="n">
-        <v>96</v>
+        <v>53</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>13.401</v>
+        <v>16.693</v>
       </c>
       <c r="I21" t="n">
-        <v>17.173</v>
+        <v>23.715</v>
       </c>
       <c r="J21" t="n">
-        <v>25.573</v>
+        <v>26.926</v>
       </c>
       <c r="K21" t="n">
-        <v>9.984999999999999</v>
+        <v>11.851</v>
       </c>
       <c r="L21" t="n">
-        <v>24.156</v>
+        <v>34.329</v>
       </c>
       <c r="M21" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="N21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="O21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P21" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="Q21" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="R21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7779078</v>
+        <v>1563175</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -12078,7 +12128,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>David Irwin</t>
+          <t>AL C SimpSimpHea</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -12087,46 +12137,46 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>13.564</v>
+        <v>13.401</v>
       </c>
       <c r="I22" t="n">
-        <v>17.485</v>
+        <v>17.173</v>
       </c>
       <c r="J22" t="n">
-        <v>22.045</v>
+        <v>25.573</v>
       </c>
       <c r="K22" t="n">
-        <v>10.226</v>
+        <v>9.984999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>25.88</v>
+        <v>24.156</v>
       </c>
       <c r="M22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="P22" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q22" t="n">
         <v>20</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>18</v>
       </c>
       <c r="R22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>6513233</v>
+        <v>7779078</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -12140,7 +12190,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim YUU </t>
+          <t>David Irwin</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -12149,46 +12199,46 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>15.963</v>
+        <v>13.564</v>
       </c>
       <c r="I23" t="n">
-        <v>19.17</v>
+        <v>17.485</v>
       </c>
       <c r="J23" t="n">
-        <v>25.752</v>
+        <v>22.045</v>
       </c>
       <c r="K23" t="n">
-        <v>11.066</v>
+        <v>10.226</v>
       </c>
       <c r="L23" t="n">
-        <v>30.865</v>
+        <v>25.88</v>
       </c>
       <c r="M23" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O23" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="P23" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="Q23" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="R23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6547311</v>
+        <v>6513233</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -12197,12 +12247,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Jimi Miralles-Lombardo</t>
+          <t xml:space="preserve">Kim YUU </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -12217,40 +12267,40 @@
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>17.216</v>
+        <v>15.963</v>
       </c>
       <c r="I24" t="n">
-        <v>20.983</v>
+        <v>19.17</v>
       </c>
       <c r="J24" t="n">
-        <v>25.134</v>
+        <v>25.752</v>
       </c>
       <c r="K24" t="n">
-        <v>10.584</v>
+        <v>11.066</v>
       </c>
       <c r="L24" t="n">
-        <v>31.082</v>
+        <v>30.865</v>
       </c>
       <c r="M24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="N24" t="n">
+        <v>16</v>
+      </c>
+      <c r="O24" t="n">
         <v>14</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q24" t="n">
         <v>16</v>
-      </c>
-      <c r="P24" t="n">
-        <v>18</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>14</v>
       </c>
       <c r="R24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>832585</v>
+        <v>6547311</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -12259,12 +12309,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>Jimi Miralles-Lombardo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12273,46 +12323,46 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="G25" t="n">
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>18.056</v>
+        <v>17.216</v>
       </c>
       <c r="I25" t="n">
-        <v>21.332</v>
+        <v>20.983</v>
       </c>
       <c r="J25" t="n">
-        <v>26.184</v>
+        <v>25.134</v>
       </c>
       <c r="K25" t="n">
-        <v>11.246</v>
+        <v>10.584</v>
       </c>
       <c r="L25" t="n">
-        <v>28.884</v>
+        <v>31.082</v>
       </c>
       <c r="M25" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" t="n">
+        <v>14</v>
+      </c>
+      <c r="O25" t="n">
         <v>16</v>
       </c>
-      <c r="N25" t="n">
-        <v>10</v>
-      </c>
-      <c r="O25" t="n">
-        <v>12</v>
-      </c>
       <c r="P25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="Q25" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="R25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2692261</v>
+        <v>832585</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -12326,7 +12376,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Murray Irons</t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12335,46 +12385,46 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G26" t="n">
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>19.477</v>
+        <v>18.056</v>
       </c>
       <c r="I26" t="n">
-        <v>21.672</v>
+        <v>21.332</v>
       </c>
       <c r="J26" t="n">
-        <v>25.876</v>
+        <v>26.184</v>
       </c>
       <c r="K26" t="n">
-        <v>11.257</v>
+        <v>11.246</v>
       </c>
       <c r="L26" t="n">
-        <v>30.39</v>
+        <v>28.884</v>
       </c>
       <c r="M26" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O26" t="n">
+        <v>12</v>
+      </c>
+      <c r="P26" t="n">
         <v>10</v>
       </c>
-      <c r="P26" t="n">
-        <v>12</v>
-      </c>
       <c r="Q26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7853050</v>
+        <v>2692261</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -12388,7 +12438,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Talyn Portman [HERC]  &amp;#6560; &amp;#127922;</t>
+          <t>Murray Irons</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -12397,46 +12447,46 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>19.041</v>
+        <v>19.477</v>
       </c>
       <c r="I27" t="n">
-        <v>21.175</v>
+        <v>21.672</v>
       </c>
       <c r="J27" t="n">
-        <v>29.912</v>
+        <v>25.876</v>
       </c>
       <c r="K27" t="n">
-        <v>13.338</v>
+        <v>11.257</v>
       </c>
       <c r="L27" t="n">
-        <v>35.68</v>
+        <v>30.39</v>
       </c>
       <c r="M27" t="n">
+        <v>14</v>
+      </c>
+      <c r="N27" t="n">
         <v>8</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
+        <v>10</v>
+      </c>
+      <c r="P27" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q27" t="n">
         <v>9</v>
-      </c>
-      <c r="O27" t="n">
-        <v>9</v>
-      </c>
-      <c r="P27" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>12</v>
       </c>
       <c r="R27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1475359</v>
+        <v>7853050</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -12450,12 +12500,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Andy Morton (TNP)</t>
+          <t>Talyn Portman [HERC]  &amp;#6560; &amp;#127922;</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -12465,98 +12515,160 @@
         <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>17.241</v>
+        <v>19.041</v>
       </c>
       <c r="I28" t="n">
-        <v>25.201</v>
+        <v>21.175</v>
       </c>
       <c r="J28" t="n">
-        <v>29.282</v>
+        <v>29.912</v>
       </c>
       <c r="K28" t="n">
-        <v>13.722</v>
+        <v>13.338</v>
       </c>
       <c r="L28" t="n">
-        <v>34.84</v>
+        <v>35.68</v>
       </c>
       <c r="M28" t="n">
+        <v>8</v>
+      </c>
+      <c r="N28" t="n">
         <v>9</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
+        <v>9</v>
+      </c>
+      <c r="P28" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q28" t="n">
         <v>12</v>
-      </c>
-      <c r="O28" t="n">
-        <v>8</v>
-      </c>
-      <c r="P28" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>8</v>
       </c>
       <c r="R28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>8233611</v>
+        <v>1475359</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Benjamin Breakfast [HERC]</t>
+          <t>Andy Morton (TNP)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="n">
+        <v>17.241</v>
+      </c>
+      <c r="I29" t="n">
+        <v>25.201</v>
+      </c>
+      <c r="J29" t="n">
+        <v>29.282</v>
+      </c>
+      <c r="K29" t="n">
+        <v>13.722</v>
+      </c>
+      <c r="L29" t="n">
+        <v>34.84</v>
+      </c>
+      <c r="M29" t="n">
+        <v>9</v>
+      </c>
+      <c r="N29" t="n">
+        <v>12</v>
+      </c>
+      <c r="O29" t="n">
+        <v>8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>8</v>
+      </c>
+      <c r="R29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>8233611</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Benjamin Breakfast [HERC]</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>100</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
         <v>19.115</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I30" t="n">
         <v>21.998</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>31.258</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K30" t="n">
         <v>13.06</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L30" t="n">
         <v>37.077</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M30" t="n">
         <v>20</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N30" t="n">
         <v>20</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O30" t="n">
         <v>20</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P30" t="n">
         <v>20</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q30" t="n">
         <v>20</v>
       </c>
-      <c r="R29" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12569,7 +12681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N29"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12896,7 +13008,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>561362</v>
+        <v>3888984</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -12905,33 +13017,33 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>The Inevitable Return of the Great White Dope</t>
+          <t>Dan Manalo (OTR)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Team CLS</t>
+          <t>OTR Racing</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>171.123</v>
+        <v>158.867</v>
       </c>
       <c r="I7" t="n">
-        <v>553.7859999999999</v>
+        <v>908.716</v>
       </c>
       <c r="J7" t="n">
-        <v>119.8</v>
+        <v>106.319</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
@@ -12940,63 +13052,63 @@
         <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>374410</v>
+        <v>561362</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Tom Ross  (TNP)</t>
+          <t>The Inevitable Return of the Great White Dope</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BIKELY</t>
+          <t>Team CLS</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>142.913</v>
+        <v>171.123</v>
       </c>
       <c r="I8" t="n">
-        <v>419.259</v>
+        <v>553.7859999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>98.758</v>
+        <v>119.8</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>619770</v>
+        <v>374410</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -13005,48 +13117,48 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert McEwan </t>
+          <t>Tom Ross  (TNP)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>BIKELY</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
         <v>2</v>
       </c>
       <c r="H9" t="n">
-        <v>125.098</v>
+        <v>142.913</v>
       </c>
       <c r="I9" t="n">
-        <v>460.473</v>
+        <v>419.259</v>
       </c>
       <c r="J9" t="n">
-        <v>91.914</v>
+        <v>98.758</v>
       </c>
       <c r="K9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1511742</v>
+        <v>619770</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -13060,7 +13172,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mark Hayes [PWCC]</t>
+          <t xml:space="preserve">Robert McEwan </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -13069,34 +13181,34 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>136.261</v>
+        <v>125.098</v>
       </c>
       <c r="I10" t="n">
-        <v>447.33</v>
+        <v>460.473</v>
       </c>
       <c r="J10" t="n">
-        <v>95.76900000000001</v>
+        <v>91.914</v>
       </c>
       <c r="K10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>372647</v>
+        <v>1511742</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -13105,48 +13217,48 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PA Persson [AAC]</t>
+          <t>Mark Hayes [PWCC]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>160.24</v>
+        <v>136.261</v>
       </c>
       <c r="I11" t="n">
-        <v>429.54</v>
+        <v>447.33</v>
       </c>
       <c r="J11" t="n">
-        <v>100.318</v>
+        <v>95.76900000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>7799511</v>
+        <v>372647</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -13160,47 +13272,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>PA Persson [AAC]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>AAC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="G12" t="n">
         <v>2</v>
       </c>
       <c r="H12" t="n">
-        <v>185.7</v>
+        <v>160.24</v>
       </c>
       <c r="I12" t="n">
-        <v>630.139</v>
+        <v>429.54</v>
       </c>
       <c r="J12" t="n">
-        <v>110.61</v>
+        <v>100.318</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>6038763</v>
+        <v>7799511</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -13210,43 +13322,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Spartacus [CVC]</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copenhagen Virtual Cycling</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="G13" t="n">
         <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>151.915</v>
+        <v>185.7</v>
       </c>
       <c r="I13" t="n">
-        <v>467.196</v>
+        <v>630.139</v>
       </c>
       <c r="J13" t="n">
-        <v>106.797</v>
+        <v>110.61</v>
       </c>
       <c r="K13" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M13" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>72072</v>
+        <v>6038763</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -13260,39 +13372,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2. Burrito &amp;#127791;</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>Spartacus [CVC]</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Copenhagen Virtual Cycling</t>
+        </is>
+      </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G14" t="n">
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>160.468</v>
+        <v>151.915</v>
       </c>
       <c r="I14" t="n">
-        <v>472.395</v>
+        <v>467.196</v>
       </c>
       <c r="J14" t="n">
-        <v>105.587</v>
+        <v>106.797</v>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M14" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>6832982</v>
+        <v>72072</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -13306,43 +13422,39 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ben WillRideForDonuts (4Star)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4STAR </t>
-        </is>
-      </c>
+          <t>2. Burrito &amp;#127791;</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G15" t="n">
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>162.714</v>
+        <v>160.468</v>
       </c>
       <c r="I15" t="n">
-        <v>470.288</v>
+        <v>472.395</v>
       </c>
       <c r="J15" t="n">
-        <v>107.283</v>
+        <v>105.587</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>4166463</v>
+        <v>6832982</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -13351,44 +13463,48 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
+          <t xml:space="preserve"> Ben WillRideForDonuts (4Star)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4STAR </t>
+        </is>
+      </c>
       <c r="F16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>160.615</v>
+        <v>162.714</v>
       </c>
       <c r="I16" t="n">
-        <v>498.638</v>
+        <v>470.288</v>
       </c>
       <c r="J16" t="n">
-        <v>106.464</v>
+        <v>107.283</v>
       </c>
       <c r="K16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>440496</v>
+        <v>4166463</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -13397,48 +13513,44 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Magnus  Andersson [SZ]</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>SZ</t>
-        </is>
-      </c>
+          <t>Corey Green (YT) GarageCycling</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
         <v>2</v>
       </c>
       <c r="H17" t="n">
-        <v>170.03</v>
+        <v>160.615</v>
       </c>
       <c r="I17" t="n">
-        <v>499.74</v>
+        <v>498.638</v>
       </c>
       <c r="J17" t="n">
-        <v>124.438</v>
+        <v>106.464</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6991072</v>
+        <v>440496</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -13447,48 +13559,48 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Jorge Fernandez Fernandez</t>
+          <t>Magnus  Andersson [SZ]</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G18" t="n">
         <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>171.461</v>
+        <v>170.03</v>
       </c>
       <c r="I18" t="n">
-        <v>523.955</v>
+        <v>499.74</v>
       </c>
       <c r="J18" t="n">
-        <v>132.531</v>
+        <v>124.438</v>
       </c>
       <c r="K18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2602856</v>
+        <v>6991072</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -13497,48 +13609,48 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
+          <t>Jorge Fernandez Fernandez</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G19" t="n">
         <v>2</v>
       </c>
       <c r="H19" t="n">
-        <v>181.116</v>
+        <v>171.461</v>
       </c>
       <c r="I19" t="n">
-        <v>526.579</v>
+        <v>523.955</v>
       </c>
       <c r="J19" t="n">
-        <v>130.284</v>
+        <v>132.531</v>
       </c>
       <c r="K19" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" t="n">
         <v>2</v>
       </c>
-      <c r="L19" t="n">
-        <v>3</v>
-      </c>
       <c r="M19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1005102</v>
+        <v>2602856</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -13552,57 +13664,57 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>195.983</v>
+        <v>181.116</v>
       </c>
       <c r="I20" t="n">
-        <v>580.78</v>
+        <v>526.579</v>
       </c>
       <c r="J20" t="n">
-        <v>156.022</v>
+        <v>130.284</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1563175</v>
+        <v>1005102</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>AL C SimpSimpHea</t>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -13611,34 +13723,34 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G21" t="n">
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>167.862</v>
+        <v>195.983</v>
       </c>
       <c r="I21" t="n">
-        <v>516.976</v>
+        <v>580.78</v>
       </c>
       <c r="J21" t="n">
-        <v>107.95</v>
+        <v>156.022</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M21" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2692261</v>
+        <v>1563175</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -13652,7 +13764,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Murray Irons</t>
+          <t>AL C SimpSimpHea</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -13661,34 +13773,34 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G22" t="n">
         <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>199.709</v>
+        <v>167.862</v>
       </c>
       <c r="I22" t="n">
-        <v>549.025</v>
+        <v>516.976</v>
       </c>
       <c r="J22" t="n">
-        <v>133.814</v>
+        <v>107.95</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>832585</v>
+        <v>2692261</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -13702,7 +13814,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>Murray Irons</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -13711,34 +13823,34 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G23" t="n">
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>197.354</v>
+        <v>199.709</v>
       </c>
       <c r="I23" t="n">
-        <v>592.653</v>
+        <v>549.025</v>
       </c>
       <c r="J23" t="n">
-        <v>135.845</v>
+        <v>133.814</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6513233</v>
+        <v>832585</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -13752,7 +13864,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim YUU </t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -13767,28 +13879,28 @@
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>198.737</v>
+        <v>197.354</v>
       </c>
       <c r="I24" t="n">
-        <v>583.885</v>
+        <v>592.653</v>
       </c>
       <c r="J24" t="n">
-        <v>154.163</v>
+        <v>135.845</v>
       </c>
       <c r="K24" t="n">
+        <v>6</v>
+      </c>
+      <c r="L24" t="n">
         <v>5</v>
       </c>
-      <c r="L24" t="n">
-        <v>4</v>
-      </c>
       <c r="M24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6547311</v>
+        <v>6513233</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -13797,12 +13909,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Jimi Miralles-Lombardo</t>
+          <t xml:space="preserve">Kim YUU </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -13811,34 +13923,34 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G25" t="n">
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>193.38</v>
+        <v>198.737</v>
       </c>
       <c r="I25" t="n">
-        <v>621.549</v>
+        <v>583.885</v>
       </c>
       <c r="J25" t="n">
-        <v>156.047</v>
+        <v>154.163</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M25" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7779078</v>
+        <v>6547311</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -13847,12 +13959,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>David Irwin</t>
+          <t>Jimi Miralles-Lombardo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -13861,34 +13973,34 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>224.666</v>
+        <v>193.38</v>
       </c>
       <c r="I26" t="n">
-        <v>593.889</v>
+        <v>621.549</v>
       </c>
       <c r="J26" t="n">
-        <v>135.629</v>
+        <v>156.047</v>
       </c>
       <c r="K26" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="L26" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" t="n">
         <v>6</v>
-      </c>
-      <c r="M26" t="n">
-        <v>8</v>
       </c>
       <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7853050</v>
+        <v>7779078</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -13902,7 +14014,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Talyn Portman [HERC]  &amp;#6560; &amp;#127922;</t>
+          <t>David Irwin</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13911,34 +14023,34 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G27" t="n">
         <v>2</v>
       </c>
       <c r="H27" t="n">
-        <v>217.754</v>
+        <v>224.666</v>
       </c>
       <c r="I27" t="n">
-        <v>609.8049999999999</v>
+        <v>593.889</v>
       </c>
       <c r="J27" t="n">
-        <v>158.831</v>
+        <v>135.629</v>
       </c>
       <c r="K27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1475359</v>
+        <v>7853050</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -13952,89 +14064,139 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Andy Morton (TNP)</t>
+          <t>Talyn Portman [HERC]  &amp;#6560; &amp;#127922;</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G28" t="n">
         <v>2</v>
       </c>
       <c r="H28" t="n">
-        <v>241.559</v>
+        <v>217.754</v>
       </c>
       <c r="I28" t="n">
-        <v>660.678</v>
+        <v>609.8049999999999</v>
       </c>
       <c r="J28" t="n">
-        <v>162.279</v>
+        <v>158.831</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>8233611</v>
+        <v>1475359</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Benjamin Breakfast [HERC]</t>
+          <t>Andy Morton (TNP)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G29" t="n">
         <v>2</v>
       </c>
       <c r="H29" t="n">
+        <v>241.559</v>
+      </c>
+      <c r="I29" t="n">
+        <v>660.678</v>
+      </c>
+      <c r="J29" t="n">
+        <v>162.279</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>8233611</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Benjamin Breakfast [HERC]</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>40</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
         <v>256.081</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I30" t="n">
         <v>701.466</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>183.092</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K30" t="n">
         <v>10</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L30" t="n">
         <v>10</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M30" t="n">
         <v>20</v>
       </c>
-      <c r="N29" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -17057,7 +17219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18305,7 +18467,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -18314,26 +18476,26 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>8325416</v>
+        <v>3888984</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PedroJ. L&amp;oacute;pez (TEZH)</t>
+          <t>Dan Manalo (OTR)</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TEZH Racing</t>
+          <t>OTR Racing</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>36:08.971</t>
+          <t>01:02:28.105</t>
         </is>
       </c>
       <c r="H34" t="n">
@@ -18352,30 +18514,30 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>374410</v>
+        <v>8325416</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Tom Ross  (TNP)</t>
+          <t>PedroJ. L&amp;oacute;pez (TEZH)</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>BIKELY</t>
+          <t>TEZH Racing</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Jnr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>37:44.825</t>
+          <t>36:08.971</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5657989</v>
+        <v>5657990</v>
       </c>
     </row>
     <row r="36">
@@ -18390,26 +18552,26 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>372647</v>
+        <v>374410</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>PA Persson [AAC]</t>
+          <t>Tom Ross  (TNP)</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AAC</t>
+          <t>BIKELY</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Jnr</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>37:54.622</t>
+          <t>37:44.825</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -18424,30 +18586,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4231019</v>
+        <v>372647</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Benjamin Leaver</t>
+          <t>PA Persson [AAC]</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>A E R O - CT</t>
+          <t>AAC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>37:59.575</t>
+          <t>37:54.622</t>
         </is>
       </c>
       <c r="H37" t="n">
@@ -18466,30 +18628,30 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>619770</v>
+        <v>4231019</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Robert McEwan </t>
+          <t>Benjamin Leaver</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>A E R O - CT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>38:17.948</t>
+          <t>37:59.575</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>5657990</v>
+        <v>5657989</v>
       </c>
     </row>
     <row r="39">
@@ -18504,11 +18666,11 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1511742</v>
+        <v>619770</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Mark Hayes [PWCC]</t>
+          <t xml:space="preserve">Robert McEwan </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -18523,7 +18685,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>38:35.101</t>
+          <t>38:17.948</t>
         </is>
       </c>
       <c r="H39" t="n">
@@ -18538,26 +18700,30 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>858008</v>
+        <v>1511742</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Florian Druguet6728</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
+          <t>Mark Hayes [PWCC]</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Team Not Pogi</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>38:36.551</t>
+          <t>38:35.101</t>
         </is>
       </c>
       <c r="H40" t="n">
@@ -18576,26 +18742,22 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1386185</v>
+        <v>858008</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Robin Wuyts [BikeRepublic]</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>BikeRepublic</t>
-        </is>
-      </c>
+          <t>Florian Druguet6728</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>38:37.382</t>
+          <t>38:36.551</t>
         </is>
       </c>
       <c r="H41" t="n">
@@ -18614,16 +18776,16 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7070492</v>
+        <v>1386185</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Daniel Carbonella</t>
+          <t>Robin Wuyts [BikeRepublic]</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SISU Racing</t>
+          <t>BikeRepublic</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -18633,7 +18795,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>38:50.357</t>
+          <t>38:37.382</t>
         </is>
       </c>
       <c r="H42" t="n">
@@ -18652,26 +18814,26 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>198785</v>
+        <v>7070492</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Deirdre Maloney</t>
+          <t>Daniel Carbonella</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HGR</t>
+          <t>SISU Racing</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>40:16.577</t>
+          <t>38:50.357</t>
         </is>
       </c>
       <c r="H43" t="n">
@@ -18690,16 +18852,16 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>7799511</v>
+        <v>198785</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>B. Copestake</t>
+          <t>Deirdre Maloney</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>HGR</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -18709,7 +18871,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>42:11.385</t>
+          <t>40:16.577</t>
         </is>
       </c>
       <c r="H44" t="n">
@@ -18719,7 +18881,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -18728,30 +18890,30 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>23982</v>
+        <v>7799511</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Esteban  Cruz</t>
+          <t>B. Copestake</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arqus</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>38:16.159</t>
+          <t>42:11.385</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>5657989</v>
+        <v>5657990</v>
       </c>
     </row>
     <row r="46">
@@ -18766,30 +18928,30 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6038763</v>
+        <v>23982</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Spartacus [CVC]</t>
+          <t>Esteban  Cruz</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Copenhagen Virtual Cycling</t>
+          <t>Arqus</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Snr</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>38:55.199</t>
+          <t>38:16.159</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>5657990</v>
+        <v>5657989</v>
       </c>
     </row>
     <row r="47">
@@ -18804,22 +18966,26 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>7229860</v>
+        <v>6038763</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Olivier Simonin</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
+          <t>Spartacus [CVC]</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Copenhagen Virtual Cycling</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Snr</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>39:11.280</t>
+          <t>38:55.199</t>
         </is>
       </c>
       <c r="H47" t="n">
@@ -18838,18 +19004,14 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>6832982</v>
+        <v>7229860</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Ben WillRideForDonuts (4Star)</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4STAR </t>
-        </is>
-      </c>
+          <t>Olivier Simonin</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
           <t>50+</t>
@@ -18857,11 +19019,11 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>40:19.333</t>
+          <t>39:11.280</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>5657989</v>
+        <v>5657990</v>
       </c>
     </row>
     <row r="49">
@@ -18876,22 +19038,26 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>72072</v>
+        <v>6832982</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2. Burrito &amp;#127791;</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
+          <t xml:space="preserve"> Ben WillRideForDonuts (4Star)</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4STAR </t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>40:21.262</t>
+          <t>40:19.333</t>
         </is>
       </c>
       <c r="H49" t="n">
@@ -18910,30 +19076,26 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>375988</v>
+        <v>72072</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Daniel Farren (TFC)</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>TFC</t>
-        </is>
-      </c>
+          <t>2. Burrito &amp;#127791;</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>40:23.099</t>
+          <t>40:21.262</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>5657990</v>
+        <v>5657989</v>
       </c>
     </row>
     <row r="51">
@@ -18948,22 +19110,26 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1481846</v>
+        <v>375988</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Tom Kwakman</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
+          <t>Daniel Farren (TFC)</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>TFC</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>40:24.841</t>
+          <t>40:23.099</t>
         </is>
       </c>
       <c r="H51" t="n">
@@ -18978,34 +19144,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>2881429</v>
+        <v>1481846</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>Tom Kwakman</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>40:25.410</t>
+          <t>40:24.841</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>5657989</v>
+        <v>5657990</v>
       </c>
     </row>
     <row r="53">
@@ -19016,26 +19178,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>7072713</v>
+        <v>2881429</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>olivier fonquerne</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
+          <t>ts &amp;#128737;&amp;#65039;[HERC]</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>40:31.291</t>
+          <t>40:25.410</t>
         </is>
       </c>
       <c r="H53" t="n">
@@ -19054,30 +19220,26 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>440496</v>
+        <v>7072713</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Magnus  Andersson [SZ]</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>SZ</t>
-        </is>
-      </c>
+          <t>olivier fonquerne</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>40:33.972</t>
+          <t>40:31.291</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>5657990</v>
+        <v>5657989</v>
       </c>
     </row>
     <row r="55">
@@ -19092,16 +19254,16 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1756745</v>
+        <v>440496</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Lotsapoppa -</t>
+          <t>Magnus  Andersson [SZ]</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GCCC</t>
+          <t>SZ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -19111,11 +19273,11 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>40:36.177</t>
+          <t>40:33.972</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>5657989</v>
+        <v>5657990</v>
       </c>
     </row>
     <row r="56">
@@ -19126,26 +19288,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>4166463</v>
+        <v>1756745</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Corey Green (YT) GarageCycling</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
+          <t>Lotsapoppa -</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>GCCC</t>
+        </is>
+      </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>40:48.138</t>
+          <t>40:36.177</t>
         </is>
       </c>
       <c r="H56" t="n">
@@ -19164,26 +19330,26 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>284495</v>
+        <v>4166463</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Matthias Runge</t>
+          <t>Corey Green (YT) GarageCycling</t>
         </is>
       </c>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>40:55.798</t>
+          <t>40:48.138</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>5657990</v>
+        <v>5657989</v>
       </c>
     </row>
     <row r="58">
@@ -19198,18 +19364,14 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>4797414</v>
+        <v>284495</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Niall McKee</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>BathCC</t>
-        </is>
-      </c>
+          <t>Matthias Runge</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
       <c r="F58" t="inlineStr">
         <is>
           <t>Vet</t>
@@ -19217,7 +19379,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>41:05.914</t>
+          <t>40:55.798</t>
         </is>
       </c>
       <c r="H58" t="n">
@@ -19232,30 +19394,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>5839285</v>
+        <v>4797414</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Ramon Plasencia (ZABI)</t>
+          <t>Niall McKee</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ZABI</t>
+          <t>BathCC</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>41:57.342</t>
+          <t>41:05.914</t>
         </is>
       </c>
       <c r="H59" t="n">
@@ -19270,34 +19432,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6991072</v>
+        <v>5839285</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Jorge Fernandez Fernandez</t>
+          <t>Ramon Plasencia (ZABI)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>ZABI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>42:08.860</t>
+          <t>41:57.342</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>5657989</v>
+        <v>5657990</v>
       </c>
     </row>
     <row r="61">
@@ -19312,26 +19474,26 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>2297188</v>
+        <v>6991072</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 Javier (HERC) </t>
+          <t>Jorge Fernandez Fernandez</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>42:38.488</t>
+          <t>42:08.860</t>
         </is>
       </c>
       <c r="H61" t="n">
@@ -19346,34 +19508,34 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2602856</v>
+        <v>2297188</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
+          <t xml:space="preserve">3 Javier (HERC) </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>42:49.270</t>
+          <t>42:38.488</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>5657990</v>
+        <v>5657989</v>
       </c>
     </row>
     <row r="63">
@@ -19388,26 +19550,26 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>937639</v>
+        <v>2602856</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Juan The One</t>
+          <t>Laurent Dumondelle&amp;#9889;[Foudre]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Team Italy</t>
+          <t>&amp;#9889;&amp;#65039;Team Foudre&amp;#9889;&amp;#65039;</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>43:07.064</t>
+          <t>42:49.270</t>
         </is>
       </c>
       <c r="H63" t="n">
@@ -19426,16 +19588,16 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>1005102</v>
+        <v>937639</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Suzie &amp;#128006;&amp;#128142;</t>
+          <t>Juan The One</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Italy</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -19445,30 +19607,30 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>43:50.311</t>
+          <t>43:07.064</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>5657989</v>
+        <v>5657990</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>1563175</v>
+        <v>1005102</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>AL C SimpSimpHea</t>
+          <t>Suzie &amp;#128006;&amp;#128142;</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -19483,7 +19645,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>42:02.210</t>
+          <t>43:50.311</t>
         </is>
       </c>
       <c r="H65" t="n">
@@ -19502,11 +19664,11 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>574469</v>
+        <v>1563175</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tracy Aldridge-Jones (HERCULES)</t>
+          <t>AL C SimpSimpHea</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -19516,12 +19678,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>42:17.661</t>
+          <t>42:02.210</t>
         </is>
       </c>
       <c r="H66" t="n">
@@ -19540,11 +19702,11 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2692261</v>
+        <v>574469</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Murray Irons</t>
+          <t>Tracy Aldridge-Jones (HERCULES)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -19554,12 +19716,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>42:33.676</t>
+          <t>42:17.661</t>
         </is>
       </c>
       <c r="H67" t="n">
@@ -19578,11 +19740,11 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>832585</v>
+        <v>2692261</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Vonita</t>
+          <t>Murray Irons</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -19592,12 +19754,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>43:17.840</t>
+          <t>42:33.676</t>
         </is>
       </c>
       <c r="H68" t="n">
@@ -19616,11 +19778,11 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7779078</v>
+        <v>832585</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>David Irwin</t>
+          <t>Vonita</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -19630,12 +19792,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>43:19.007</t>
+          <t>43:17.840</t>
         </is>
       </c>
       <c r="H69" t="n">
@@ -19654,11 +19816,11 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>4747461</v>
+        <v>7779078</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Andrew Carrington</t>
+          <t>David Irwin</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -19668,12 +19830,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>43:40.113</t>
+          <t>43:19.007</t>
         </is>
       </c>
       <c r="H70" t="n">
@@ -19692,11 +19854,11 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>6513233</v>
+        <v>4747461</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kim YUU </t>
+          <t>Andrew Carrington</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -19706,12 +19868,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>43:53.856</t>
+          <t>43:40.113</t>
         </is>
       </c>
       <c r="H71" t="n">
@@ -19730,11 +19892,11 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>1379058</v>
+        <v>6513233</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>david white (HERC)</t>
+          <t xml:space="preserve">Kim YUU </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -19744,12 +19906,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>44:11.975</t>
+          <t>43:53.856</t>
         </is>
       </c>
       <c r="H72" t="n">
@@ -19764,34 +19926,34 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7943300</v>
+        <v>1379058</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Conor Wall</t>
+          <t>david white (HERC)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Team RWB</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Jnr</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>44:21.104</t>
+          <t>44:11.975</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>5657990</v>
+        <v>5657989</v>
       </c>
     </row>
     <row r="74">
@@ -19802,26 +19964,30 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>7696515</v>
+        <v>7943300</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>kevan thompson</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
+          <t>Conor Wall</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Team RWB</t>
+        </is>
+      </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Jnr</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>44:28.142</t>
+          <t>44:21.104</t>
         </is>
       </c>
       <c r="H74" t="n">
@@ -19836,34 +20002,30 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>6547311</v>
+        <v>7696515</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Jimi Miralles-Lombardo</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>kevan thompson</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mas</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>44:31.433</t>
+          <t>44:28.142</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>5657989</v>
+        <v>5657990</v>
       </c>
     </row>
     <row r="76">
@@ -19874,34 +20036,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3145714</v>
+        <v>6547311</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Peter Rosenqvist [SZR]</t>
+          <t>Jimi Miralles-Lombardo</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>SZR</t>
+          <t>HERC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Mas</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>44:48.125</t>
+          <t>44:31.433</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>5657990</v>
+        <v>5657989</v>
       </c>
     </row>
     <row r="77">
@@ -19916,26 +20078,26 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>1475359</v>
+        <v>3145714</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Andy Morton (TNP)</t>
+          <t>Peter Rosenqvist [SZR]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Team Not Pogi</t>
+          <t>SZR</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>50+</t>
+          <t>60+</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>46:15.569</t>
+          <t>44:48.125</t>
         </is>
       </c>
       <c r="H77" t="n">
@@ -19954,16 +20116,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7853050</v>
+        <v>1475359</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Talyn Portman [HERC]  &amp;#6560; &amp;#127922;</t>
+          <t>Andy Morton (TNP)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>HERC</t>
+          <t>Team Not Pogi</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -19973,11 +20135,11 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>46:39.647</t>
+          <t>46:15.569</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>5657989</v>
+        <v>5657990</v>
       </c>
     </row>
     <row r="79">
@@ -19992,22 +20154,26 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>2288977</v>
+        <v>7853050</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>H Suzu&amp;#128150;</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr"/>
+          <t>Talyn Portman 5 [HERC] &amp;#9854;</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>50+</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>50:42.826</t>
+          <t>46:39.647</t>
         </is>
       </c>
       <c r="H79" t="n">
@@ -20017,35 +20183,31 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8233611</v>
+        <v>2288977</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Benjamin Breakfast [HERC]</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>HERC</t>
-        </is>
-      </c>
+          <t>H Suzu&amp;#128150;</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vet</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>50:00.759</t>
+          <t>50:42.826</t>
         </is>
       </c>
       <c r="H80" t="n">
@@ -20064,22 +20226,26 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>6492269</v>
+        <v>8233611</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Lars P. Mikkelsen</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
+          <t>Benjamin Breakfast [HERC]</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>HERC</t>
+        </is>
+      </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60+</t>
+          <t>Vet</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>52:20.565</t>
+          <t>50:00.759</t>
         </is>
       </c>
       <c r="H81" t="n">
@@ -20098,29 +20264,63 @@
         </is>
       </c>
       <c r="C82" t="n">
+        <v>6492269</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Lars P. Mikkelsen</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>60+</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>52:20.565</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>5657989</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
         <v>5156484</v>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>Alex (3R/TV)</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>Race3R</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>Jnr</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>54:18.616</t>
         </is>
       </c>
-      <c r="H82" t="n">
+      <c r="H83" t="n">
         <v>5657990</v>
       </c>
     </row>
